--- a/plans/receipts-001.xlsx
+++ b/plans/receipts-001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Desktop\My Files\Website Projects\tc-ventures site\plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A5892F3-3A40-4738-ADFE-E2322CB86EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4616BE6-2208-483F-88A1-772296D2EB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to rule" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="711">
   <si>
     <t>ID</t>
   </si>
@@ -2152,6 +2152,15 @@
   </si>
   <si>
     <t>Thomas, 2026-09-23: GPRS was built before he used Claude Code or Cowork; there were no handoffs, so there is no session record to mine. R-001–R-003 (the March 2026 audits) are the pre-method record; R-006–R-008 are from after.</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>CUT</t>
+  </si>
+  <si>
+    <t>cut]</t>
   </si>
 </sst>
 </file>
@@ -2691,9 +2700,9 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="40" customWidth="1"/>
   </cols>
@@ -2736,7 +2745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="102" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -2767,10 +2776,12 @@
       <c r="J2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="6"/>
+      <c r="K2" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="102" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -2801,7 +2812,9 @@
       <c r="J3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="6"/>
+      <c r="K3" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -2835,10 +2848,12 @@
       <c r="J4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="6"/>
+      <c r="K4" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>37</v>
       </c>
@@ -2867,10 +2882,12 @@
         <v>20</v>
       </c>
       <c r="J5" s="5"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
@@ -2899,10 +2916,12 @@
         <v>20</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="6"/>
+      <c r="K6" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>49</v>
       </c>
@@ -2931,10 +2950,12 @@
         <v>20</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>56</v>
       </c>
@@ -2965,10 +2986,12 @@
       <c r="J8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="6"/>
+      <c r="K8" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>64</v>
       </c>
@@ -2997,10 +3020,12 @@
         <v>20</v>
       </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>68</v>
       </c>
@@ -3031,7 +3056,9 @@
       <c r="J10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="6"/>
+      <c r="K10" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3063,10 +3090,12 @@
         <v>20</v>
       </c>
       <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
@@ -3095,7 +3124,9 @@
         <v>20</v>
       </c>
       <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3127,10 +3158,12 @@
         <v>20</v>
       </c>
       <c r="J13" s="5"/>
-      <c r="K13" s="6"/>
+      <c r="K13" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>88</v>
       </c>
@@ -3159,10 +3192,12 @@
         <v>20</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>94</v>
       </c>
@@ -3191,7 +3226,9 @@
         <v>20</v>
       </c>
       <c r="J15" s="5"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L15" s="6"/>
     </row>
     <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3223,7 +3260,9 @@
         <v>20</v>
       </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="6"/>
+      <c r="K16" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3255,7 +3294,9 @@
         <v>20</v>
       </c>
       <c r="J17" s="5"/>
-      <c r="K17" s="6"/>
+      <c r="K17" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3287,7 +3328,9 @@
         <v>20</v>
       </c>
       <c r="J18" s="5"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L18" s="6"/>
     </row>
     <row r="19" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -3319,10 +3362,12 @@
         <v>20</v>
       </c>
       <c r="J19" s="5"/>
-      <c r="K19" s="6"/>
+      <c r="K19" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>120</v>
       </c>
@@ -3351,10 +3396,12 @@
         <v>20</v>
       </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>125</v>
       </c>
@@ -3383,7 +3430,9 @@
         <v>20</v>
       </c>
       <c r="J21" s="5"/>
-      <c r="K21" s="6"/>
+      <c r="K21" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3415,7 +3464,9 @@
         <v>20</v>
       </c>
       <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3447,7 +3498,9 @@
         <v>20</v>
       </c>
       <c r="J23" s="5"/>
-      <c r="K23" s="6"/>
+      <c r="K23" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3479,7 +3532,9 @@
         <v>20</v>
       </c>
       <c r="J24" s="5"/>
-      <c r="K24" s="6"/>
+      <c r="K24" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3511,10 +3566,12 @@
         <v>20</v>
       </c>
       <c r="J25" s="5"/>
-      <c r="K25" s="6"/>
+      <c r="K25" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>152</v>
       </c>
@@ -3543,10 +3600,12 @@
         <v>158</v>
       </c>
       <c r="J26" s="5"/>
-      <c r="K26" s="6"/>
+      <c r="K26" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>159</v>
       </c>
@@ -3575,7 +3634,9 @@
         <v>20</v>
       </c>
       <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3609,10 +3670,12 @@
       <c r="J28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="6"/>
+      <c r="K28" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>170</v>
       </c>
@@ -3643,7 +3706,9 @@
       <c r="J29" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K29" s="6"/>
+      <c r="K29" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3677,7 +3742,9 @@
       <c r="J30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="6"/>
+      <c r="K30" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -3711,10 +3778,12 @@
       <c r="J31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K31" s="6"/>
+      <c r="K31" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>184</v>
       </c>
@@ -3745,10 +3814,12 @@
       <c r="J32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="6"/>
+      <c r="K32" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>190</v>
       </c>
@@ -3779,10 +3850,12 @@
       <c r="J33" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K33" s="6"/>
+      <c r="K33" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="102" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>195</v>
       </c>
@@ -3813,7 +3886,9 @@
       <c r="J34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K34" s="6"/>
+      <c r="K34" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L34" s="6"/>
     </row>
     <row r="35" spans="1:12" ht="51" x14ac:dyDescent="0.25">
@@ -3845,7 +3920,9 @@
         <v>20</v>
       </c>
       <c r="J35" s="5"/>
-      <c r="K35" s="6"/>
+      <c r="K35" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -3877,7 +3954,9 @@
         <v>20</v>
       </c>
       <c r="J36" s="5"/>
-      <c r="K36" s="6"/>
+      <c r="K36" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L36" s="6"/>
     </row>
     <row r="37" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -3909,7 +3988,9 @@
         <v>20</v>
       </c>
       <c r="J37" s="5"/>
-      <c r="K37" s="6"/>
+      <c r="K37" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L37" s="6"/>
     </row>
     <row r="38" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -3943,10 +4024,12 @@
       <c r="J38" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K38" s="6"/>
+      <c r="K38" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>223</v>
       </c>
@@ -3975,7 +4058,9 @@
         <v>20</v>
       </c>
       <c r="J39" s="5"/>
-      <c r="K39" s="6"/>
+      <c r="K39" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L39" s="6"/>
     </row>
     <row r="40" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4007,7 +4092,9 @@
         <v>20</v>
       </c>
       <c r="J40" s="5"/>
-      <c r="K40" s="6"/>
+      <c r="K40" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L40" s="6"/>
     </row>
     <row r="41" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4039,10 +4126,12 @@
         <v>240</v>
       </c>
       <c r="J41" s="5"/>
-      <c r="K41" s="6"/>
+      <c r="K41" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>241</v>
       </c>
@@ -4071,7 +4160,9 @@
         <v>20</v>
       </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="6"/>
+      <c r="K42" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L42" s="6"/>
     </row>
     <row r="43" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4103,7 +4194,9 @@
         <v>20</v>
       </c>
       <c r="J43" s="5"/>
-      <c r="K43" s="6"/>
+      <c r="K43" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4137,7 +4230,9 @@
       <c r="J44" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K44" s="6"/>
+      <c r="K44" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L44" s="6"/>
     </row>
     <row r="45" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4169,7 +4264,9 @@
         <v>20</v>
       </c>
       <c r="J45" s="5"/>
-      <c r="K45" s="6"/>
+      <c r="K45" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" ht="51" x14ac:dyDescent="0.25">
@@ -4203,10 +4300,12 @@
       <c r="J46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K46" s="6"/>
+      <c r="K46" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>268</v>
       </c>
@@ -4235,7 +4334,9 @@
         <v>20</v>
       </c>
       <c r="J47" s="5"/>
-      <c r="K47" s="6"/>
+      <c r="K47" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L47" s="6"/>
     </row>
     <row r="48" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4267,7 +4368,9 @@
         <v>20</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="6"/>
+      <c r="K48" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4299,10 +4402,12 @@
         <v>240</v>
       </c>
       <c r="J49" s="5"/>
-      <c r="K49" s="6"/>
+      <c r="K49" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>283</v>
       </c>
@@ -4331,10 +4436,12 @@
         <v>20</v>
       </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="6"/>
+      <c r="K50" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>288</v>
       </c>
@@ -4363,7 +4470,9 @@
         <v>20</v>
       </c>
       <c r="J51" s="5"/>
-      <c r="K51" s="6"/>
+      <c r="K51" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4395,7 +4504,9 @@
         <v>240</v>
       </c>
       <c r="J52" s="5"/>
-      <c r="K52" s="6"/>
+      <c r="K52" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4427,7 +4538,9 @@
         <v>240</v>
       </c>
       <c r="J53" s="5"/>
-      <c r="K53" s="6"/>
+      <c r="K53" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L53" s="6"/>
     </row>
     <row r="54" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4459,10 +4572,12 @@
         <v>20</v>
       </c>
       <c r="J54" s="5"/>
-      <c r="K54" s="6"/>
+      <c r="K54" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>309</v>
       </c>
@@ -4493,10 +4608,12 @@
       <c r="J55" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K55" s="6"/>
+      <c r="K55" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>313</v>
       </c>
@@ -4527,7 +4644,9 @@
       <c r="J56" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K56" s="6"/>
+      <c r="K56" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L56" s="6"/>
     </row>
     <row r="57" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4559,10 +4678,12 @@
         <v>20</v>
       </c>
       <c r="J57" s="5"/>
-      <c r="K57" s="6"/>
+      <c r="K57" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="102" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>324</v>
       </c>
@@ -4591,10 +4712,12 @@
         <v>330</v>
       </c>
       <c r="J58" s="5"/>
-      <c r="K58" s="6"/>
+      <c r="K58" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>331</v>
       </c>
@@ -4623,7 +4746,9 @@
         <v>335</v>
       </c>
       <c r="J59" s="5"/>
-      <c r="K59" s="6"/>
+      <c r="K59" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L59" s="6"/>
     </row>
     <row r="60" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4655,7 +4780,9 @@
         <v>20</v>
       </c>
       <c r="J60" s="5"/>
-      <c r="K60" s="6"/>
+      <c r="K60" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L60" s="6"/>
     </row>
     <row r="61" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4687,7 +4814,9 @@
         <v>20</v>
       </c>
       <c r="J61" s="5"/>
-      <c r="K61" s="6"/>
+      <c r="K61" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4719,10 +4848,12 @@
         <v>20</v>
       </c>
       <c r="J62" s="5"/>
-      <c r="K62" s="6"/>
+      <c r="K62" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>351</v>
       </c>
@@ -4751,7 +4882,9 @@
         <v>20</v>
       </c>
       <c r="J63" s="5"/>
-      <c r="K63" s="6"/>
+      <c r="K63" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L63" s="6"/>
     </row>
     <row r="64" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4785,10 +4918,12 @@
       <c r="J64" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K64" s="6"/>
+      <c r="K64" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>361</v>
       </c>
@@ -4817,10 +4952,12 @@
         <v>335</v>
       </c>
       <c r="J65" s="5"/>
-      <c r="K65" s="6"/>
+      <c r="K65" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>366</v>
       </c>
@@ -4851,10 +4988,12 @@
       <c r="J66" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K66" s="6"/>
+      <c r="K66" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>371</v>
       </c>
@@ -4883,7 +5022,9 @@
         <v>20</v>
       </c>
       <c r="J67" s="5"/>
-      <c r="K67" s="6"/>
+      <c r="K67" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L67" s="6"/>
     </row>
     <row r="68" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4915,10 +5056,12 @@
         <v>20</v>
       </c>
       <c r="J68" s="5"/>
-      <c r="K68" s="6"/>
+      <c r="K68" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>382</v>
       </c>
@@ -4947,7 +5090,9 @@
         <v>20</v>
       </c>
       <c r="J69" s="5"/>
-      <c r="K69" s="6"/>
+      <c r="K69" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L69" s="6"/>
     </row>
     <row r="70" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -4979,7 +5124,9 @@
         <v>20</v>
       </c>
       <c r="J70" s="5"/>
-      <c r="K70" s="6"/>
+      <c r="K70" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5013,7 +5160,9 @@
       <c r="J71" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K71" s="6"/>
+      <c r="K71" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L71" s="6"/>
     </row>
     <row r="72" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5045,7 +5194,9 @@
         <v>20</v>
       </c>
       <c r="J72" s="5"/>
-      <c r="K72" s="6"/>
+      <c r="K72" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L72" s="6"/>
     </row>
     <row r="73" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5077,7 +5228,9 @@
         <v>20</v>
       </c>
       <c r="J73" s="5"/>
-      <c r="K73" s="6"/>
+      <c r="K73" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L73" s="6"/>
     </row>
     <row r="74" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5109,7 +5262,9 @@
         <v>20</v>
       </c>
       <c r="J74" s="5"/>
-      <c r="K74" s="6"/>
+      <c r="K74" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L74" s="6"/>
     </row>
     <row r="75" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5141,7 +5296,9 @@
         <v>20</v>
       </c>
       <c r="J75" s="5"/>
-      <c r="K75" s="6"/>
+      <c r="K75" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L75" s="6"/>
     </row>
     <row r="76" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5173,7 +5330,9 @@
         <v>20</v>
       </c>
       <c r="J76" s="5"/>
-      <c r="K76" s="6"/>
+      <c r="K76" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L76" s="6"/>
     </row>
     <row r="77" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5205,7 +5364,9 @@
         <v>20</v>
       </c>
       <c r="J77" s="5"/>
-      <c r="K77" s="6"/>
+      <c r="K77" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L77" s="6"/>
     </row>
     <row r="78" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5239,7 +5400,9 @@
       <c r="J78" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K78" s="6"/>
+      <c r="K78" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L78" s="6"/>
     </row>
     <row r="79" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5271,10 +5434,12 @@
         <v>20</v>
       </c>
       <c r="J79" s="5"/>
-      <c r="K79" s="6"/>
+      <c r="K79" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>440</v>
       </c>
@@ -5303,7 +5468,9 @@
         <v>446</v>
       </c>
       <c r="J80" s="5"/>
-      <c r="K80" s="6"/>
+      <c r="K80" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L80" s="6"/>
     </row>
     <row r="81" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5335,10 +5502,12 @@
         <v>335</v>
       </c>
       <c r="J81" s="5"/>
-      <c r="K81" s="6"/>
+      <c r="K81" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>451</v>
       </c>
@@ -5367,7 +5536,9 @@
         <v>20</v>
       </c>
       <c r="J82" s="5"/>
-      <c r="K82" s="6"/>
+      <c r="K82" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L82" s="6"/>
     </row>
     <row r="83" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5399,7 +5570,9 @@
         <v>20</v>
       </c>
       <c r="J83" s="5"/>
-      <c r="K83" s="6"/>
+      <c r="K83" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L83" s="6"/>
     </row>
     <row r="84" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5431,10 +5604,12 @@
         <v>20</v>
       </c>
       <c r="J84" s="5"/>
-      <c r="K84" s="6"/>
+      <c r="K84" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>465</v>
       </c>
@@ -5463,7 +5638,9 @@
         <v>20</v>
       </c>
       <c r="J85" s="5"/>
-      <c r="K85" s="6"/>
+      <c r="K85" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L85" s="6"/>
     </row>
     <row r="86" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5495,10 +5672,12 @@
         <v>20</v>
       </c>
       <c r="J86" s="5"/>
-      <c r="K86" s="6"/>
+      <c r="K86" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>477</v>
       </c>
@@ -5527,10 +5706,12 @@
         <v>20</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="6"/>
+      <c r="K87" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>483</v>
       </c>
@@ -5559,7 +5740,9 @@
         <v>20</v>
       </c>
       <c r="J88" s="5"/>
-      <c r="K88" s="6"/>
+      <c r="K88" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L88" s="6"/>
     </row>
     <row r="89" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5591,10 +5774,12 @@
         <v>20</v>
       </c>
       <c r="J89" s="5"/>
-      <c r="K89" s="6"/>
+      <c r="K89" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>494</v>
       </c>
@@ -5623,10 +5808,12 @@
         <v>20</v>
       </c>
       <c r="J90" s="5"/>
-      <c r="K90" s="6"/>
+      <c r="K90" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>500</v>
       </c>
@@ -5655,10 +5842,12 @@
         <v>20</v>
       </c>
       <c r="J91" s="5"/>
-      <c r="K91" s="6"/>
+      <c r="K91" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>505</v>
       </c>
@@ -5687,10 +5876,12 @@
         <v>20</v>
       </c>
       <c r="J92" s="5"/>
-      <c r="K92" s="6"/>
+      <c r="K92" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>510</v>
       </c>
@@ -5719,10 +5910,12 @@
         <v>20</v>
       </c>
       <c r="J93" s="5"/>
-      <c r="K93" s="6"/>
+      <c r="K93" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>515</v>
       </c>
@@ -5751,7 +5944,9 @@
         <v>20</v>
       </c>
       <c r="J94" s="5"/>
-      <c r="K94" s="6"/>
+      <c r="K94" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L94" s="6"/>
     </row>
     <row r="95" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5783,10 +5978,12 @@
         <v>20</v>
       </c>
       <c r="J95" s="5"/>
-      <c r="K95" s="6"/>
+      <c r="K95" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>526</v>
       </c>
@@ -5815,7 +6012,9 @@
         <v>20</v>
       </c>
       <c r="J96" s="5"/>
-      <c r="K96" s="6"/>
+      <c r="K96" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L96" s="6"/>
     </row>
     <row r="97" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -5847,7 +6046,9 @@
         <v>20</v>
       </c>
       <c r="J97" s="5"/>
-      <c r="K97" s="6"/>
+      <c r="K97" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L97" s="6"/>
     </row>
     <row r="98" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5879,10 +6080,12 @@
         <v>20</v>
       </c>
       <c r="J98" s="5"/>
-      <c r="K98" s="6"/>
+      <c r="K98" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>543</v>
       </c>
@@ -5911,7 +6114,9 @@
         <v>20</v>
       </c>
       <c r="J99" s="5"/>
-      <c r="K99" s="6"/>
+      <c r="K99" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5943,7 +6148,9 @@
         <v>20</v>
       </c>
       <c r="J100" s="5"/>
-      <c r="K100" s="6"/>
+      <c r="K100" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -5975,7 +6182,9 @@
         <v>20</v>
       </c>
       <c r="J101" s="5"/>
-      <c r="K101" s="6"/>
+      <c r="K101" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L101" s="6"/>
     </row>
     <row r="102" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -6007,7 +6216,9 @@
         <v>20</v>
       </c>
       <c r="J102" s="5"/>
-      <c r="K102" s="6"/>
+      <c r="K102" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L102" s="6"/>
     </row>
     <row r="103" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -6041,7 +6252,9 @@
       <c r="J103" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K103" s="6"/>
+      <c r="K103" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L103" s="6"/>
     </row>
     <row r="104" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
@@ -6075,10 +6288,12 @@
       <c r="J104" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K104" s="6"/>
+      <c r="K104" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L104" s="6"/>
     </row>
-    <row r="105" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>576</v>
       </c>
@@ -6107,10 +6322,12 @@
         <v>20</v>
       </c>
       <c r="J105" s="5"/>
-      <c r="K105" s="6"/>
+      <c r="K105" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>581</v>
       </c>
@@ -6141,10 +6358,12 @@
       <c r="J106" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K106" s="6"/>
+      <c r="K106" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L106" s="6"/>
     </row>
-    <row r="107" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>588</v>
       </c>
@@ -6173,10 +6392,12 @@
         <v>20</v>
       </c>
       <c r="J107" s="5"/>
-      <c r="K107" s="6"/>
+      <c r="K107" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L107" s="6"/>
     </row>
-    <row r="108" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="102" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>594</v>
       </c>
@@ -6207,10 +6428,12 @@
       <c r="J108" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K108" s="6"/>
+      <c r="K108" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L108" s="6"/>
     </row>
-    <row r="109" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>599</v>
       </c>
@@ -6239,10 +6462,12 @@
         <v>20</v>
       </c>
       <c r="J109" s="5"/>
-      <c r="K109" s="6"/>
+      <c r="K109" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>604</v>
       </c>
@@ -6271,7 +6496,9 @@
         <v>20</v>
       </c>
       <c r="J110" s="5"/>
-      <c r="K110" s="6"/>
+      <c r="K110" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L110" s="6"/>
     </row>
     <row r="111" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -6303,7 +6530,9 @@
         <v>20</v>
       </c>
       <c r="J111" s="5"/>
-      <c r="K111" s="6"/>
+      <c r="K111" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L111" s="6"/>
     </row>
     <row r="112" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
@@ -6335,10 +6564,12 @@
         <v>20</v>
       </c>
       <c r="J112" s="5"/>
-      <c r="K112" s="6"/>
+      <c r="K112" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="L112" s="6"/>
     </row>
-    <row r="113" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>619</v>
       </c>
@@ -6367,7 +6598,9 @@
         <v>20</v>
       </c>
       <c r="J113" s="5"/>
-      <c r="K113" s="6"/>
+      <c r="K113" s="6" t="s">
+        <v>708</v>
+      </c>
       <c r="L113" s="6"/>
     </row>
   </sheetData>
@@ -6427,7 +6660,9 @@
       <c r="D2" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -6443,7 +6678,9 @@
       <c r="D3" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
@@ -6459,7 +6696,9 @@
       <c r="D4" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -6475,7 +6714,9 @@
       <c r="D5" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6491,7 +6732,9 @@
       <c r="D6" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -6507,7 +6750,9 @@
       <c r="D7" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -6523,7 +6768,9 @@
       <c r="D8" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -6539,7 +6786,9 @@
       <c r="D9" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,7 +6804,9 @@
       <c r="D10" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6571,7 +6822,9 @@
       <c r="D11" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -6587,7 +6840,9 @@
       <c r="D12" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>709</v>
+      </c>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -6603,7 +6858,9 @@
       <c r="D13" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>710</v>
+      </c>
       <c r="F13" s="6"/>
     </row>
   </sheetData>
